--- a/output/pdf_financials_xlsx/OBUL.xlsx
+++ b/output/pdf_financials_xlsx/OBUL.xlsx
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.243912</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>5.967137</v>
       </c>
     </row>
     <row r="93">
@@ -2730,7 +2730,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>2.243912</v>
       </c>

--- a/output/pdf_financials_xlsx/OBUL.xlsx
+++ b/output/pdf_financials_xlsx/OBUL.xlsx
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000639</v>
       </c>
     </row>
     <row r="13">
@@ -785,7 +785,7 @@
         <v>-4.384626</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.593708</v>
+        <v>-3.594347</v>
       </c>
     </row>
     <row r="28">
@@ -811,7 +811,7 @@
         <v>-4.344919</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.564305</v>
+        <v>-3.564944</v>
       </c>
     </row>
     <row r="30">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.027295</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.631532</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.027295</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>3.045452</v>
+        <v>7.676984</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.207455</v>
+        <v>0.18016</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.107367</v>
+        <v>0.475835</v>
       </c>
     </row>
     <row r="49">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">

--- a/output/pdf_financials_xlsx/OBUL.xlsx
+++ b/output/pdf_financials_xlsx/OBUL.xlsx
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.005134</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.028846</v>
       </c>
     </row>
     <row r="111">
@@ -2894,7 +2894,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.005134</v>
       </c>
